--- a/tests/test_config.xlsx
+++ b/tests/test_config.xlsx
@@ -132,8 +132,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblTestExpected" displayName="tblTestExpected" ref="A1:J25" headerRowCount="1">
-  <autoFilter ref="A1:J25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblTestExpected" displayName="tblTestExpected" ref="A1:J26" headerRowCount="1">
+  <autoFilter ref="A1:J26"/>
   <tableColumns count="10">
     <tableColumn id="1" name="SourceID"/>
     <tableColumn id="2" name="Status"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -465,7 +465,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Етап C: регресійні тести Power Query Engine (v4.5)</t>
+          <t># Регресійні тести Engine</t>
         </is>
       </c>
     </row>
@@ -475,111 +475,111 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ЩО ЦЕ. Окрема тестова книга (копія Engine) з власним реєстром, що вказує на теку з маленькими тестовими файлами з відомим результатом. Одне оновлення книги перевіряє 24 джерела у зведенні якості і 25 сценаріїв завантаження. Перед кожною зміною коду Engine запустіть тести; після зміни вони мають лишитися зеленими.</t>
+          <t>| Що | Опис |</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>| --- | --- |</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ПІДГОТОВКА (один раз, автоматично)</t>
+          <t>| fixtures\ | 21 тестовий файл (C… — CSV, X… — Excel і непідтримуваний формат, N01 — файл без схеми), кожен із відомим результатом |</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. Розпакуйте архів пакета в постійне місце, наприклад D:\EngineTests. Тека fixtures має лишатися там: шляхи до тестових файлів записуються в реєстр тестової книги.</t>
+          <t>| test_config.xlsx | Призначення, реєстр, схема, фільтри й очікування тестової книги (аркуші «Реєстр», «Схема», «Фільтри», «Призначення», «Очікування», «Навантаження») |</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2. Відкрийте test_engine\TEST_POWER_QUERY_ENGINE.xlsm (або іншу КОПІЮ робочої книги Engine).</t>
+          <t>| queries\ | Тестові запити test_*.pq (test_All збирає 11 наборів) |</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3. Редактор VBA (Alt+F11) &gt; File &gt; Import File: engine\vba\modSetupTestEngine.bas.</t>
+          <t>| gen_fixtures.py | Генератор fixtures\ і test_config.xlsx |</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>4. Запустіть макрос SetupTestEngine (Alt+F8) і виберіть розпаковану теку пакета (ту, де лежать теки engine і test_engine).</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Макрос: додає тестові призначення в tblTargetType; замінює рядки tblSourceRegistry (з Path = тека fixtures), tblSchemaRegistry, tblRowFilters; очищає tblDefaultHeaders; створює tblTestExpected і tblTestLoad; імпортує всі запити з engine\powerquery (Engine v4.5 і тести); завантажує test_All, test_Summary, test_Load на аркуш «Тести».</t>
+          <t>## Як підготувати тестову книгу з репозиторію</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>5. Дані &gt; Оновити все. Збережіть книгу.</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Повторний запуск SetupTestEngine безпечний: тестові дані й запити просто перезаписуються (так само оновлюється код Engine у тестовій книзі після нових патчів).</t>
+          <t>1. Скопіюйте робочу книгу **поза репозиторій** (наприклад, D:\EngineTests\TEST_PQ_ENGINE.xlsm).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2. Редактор VBA (Alt+F11) → File → Import File: `powerquery\vba\modSetupTestEngine.bas` (і modEngineCommon, якщо його ще немає).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ПІДГОТОВКА ВРУЧНУ (якщо макрос не підходить)</t>
+          <t>3. Запустіть SetupTestEngine (Alt+F8) і виберіть **корінь клону репозиторію**. Макрос розпізнає структуру репозиторію:</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- tblTargetType: додати рядки з аркуша «Призначення» файла test_config.xlsx.</t>
+          <t xml:space="preserve">   бере конфігурацію з tests\test_config.xlsx, фікстури з tests\fixtures, запити Engine з powerquery\queries і тести з tests\queries.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- tblSourceRegistry: видалити всі рядки, вставити рядки з аркуша «Реєстр» (без колонки «Опис»); у Path для всіх рядків повний шлях до теки fixtures. Колонка ErrorThreshold має бути в таблиці.</t>
+          <t xml:space="preserve">   Якщо не знайдено жодного .pq або немає test_All, він зупиняється з помилкою.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- tblSchemaRegistry і tblRowFilters: замінити рядками з аркушів «Схема» і «Фільтри»; tblDefaultHeaders очистити.</t>
+          <t>4. Дані → Оновити все. На аркуші «Тести» таблиця test_All: кожен рядок — PASS.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>- Скопіювати в книгу аркуші «Очікування» і «Навантаження» (таблиці tblTestExpected і tblTestLoad).</t>
+          <t xml:space="preserve">   Деталі FAIL — у test_Summary і test_Load (вони лише підключення; тимчасово завантажте потрібний на окремий аркуш).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>- Імпортувати engine\powerquery макросом ImportPQQueriesFromFolder; test_All, test_Summary, test_Load завантажити на аркуш, src_TestExpected лише підключення.</t>
+          <t>5. Збережіть книгу і запустіть UpdateHelp. ExportPowerQueriesToRepo у тестовій книзі не запускайте (він і сам зупиниться).</t>
         </is>
       </c>
     </row>
@@ -589,59 +589,55 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ЗАПУСК</t>
+          <t>Той самий макрос працює і з пакетом Engine (теки engine, test_engine).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Дані &gt; Оновити все. Аркуш «Тести»: у test_All кожен рядок має Result = PASS.</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Якщо є FAIL: test_Summary і test_Load показують кожну перевірку з очікуваним і фактичним значенням (рядки з Pass = FALSE угорі test_Summary).</t>
+          <t>## Фікстури і генератор</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cfgSettings у тестовій книзі не змінюйте: тести очікують ErrorPolicy = Report, ErrorThreshold = null, CsvEncoding = 1251.</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>`python gen_fixtures.py &lt;тека&gt;` створює `&lt;тека&gt;\fixtures\` і `&lt;тека&gt;\test_config.xlsx` (потрібен openpyxl).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ЩО ПЕРЕВІРЯЄТЬСЯ</t>
+          <t>Аркуш «Інструкція» в test_config.xlsx — текст цього README.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>test_Summary порівнює pq_QualitySummary з tblTestExpected. Порожня клітинка очікування не перевіряється, «-» означає «очікується порожнє значення», Status = ABSENT означає, що джерела не має бути у зведенні.</t>
+          <t>CSV виходять байт у байт однаковими; файли .xlsx — з іншою датою створення всередині, тож Git покаже їх зміненими,</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>test_Load для кожного рядка tblTestLoad викликає fn_ReadPurpose лише для вказаних SourceID (кілька через кому) і перевіряє: пройшло завантаження (OK) чи зупинилося (ERROR), код причини (Reason), кількість рядків і клітинок з помилками.</t>
+          <t>хоча вміст той самий. Тому перегенеровувати лише тоді, коли змінився сам генератор, і комітити генератор і файли разом.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>test_All збирає підсумок test_Summary, test_Load, test_ToRate, test_Canon і test_RowFilters.</t>
+          <t>Фікстури навмисно мають різні кодування, закінчення рядків і «пошкоджені» файли: .gitattributes зберігає їх байт у байт.</t>
         </is>
       </c>
     </row>
@@ -651,52 +647,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ЯК ДОДАТИ СЦЕНАРІЙ</t>
+          <t>## Як додати сценарій</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Новий файл у теку fixtures, рядок у tblSourceRegistry, рядок очікувань у tblTestExpected і, за потреби, рядок у tblTestLoad. Код запитів не змінюється. Щоб сценарій пережив повторний SetupTestEngine, додайте його й у test_config.xlsx (або в tools\gen_fixtures.py).</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Новий блок у gen_fixtures.py (файл, рядок реєстру, очікування) → перегенерувати → SetupTestEngine у тестовій книзі.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ВАЖЛИВО</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>- Тестова книга не для роботи з реальними даними: її реєстр і схема тестові.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>- pq_RegistryCheck у тестовій книзі навмисно показує дубль періоду (C01 і C16) і дубль файлу (C01 і C17): це сценарії L17 і L18.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>- Очікування C13 (UTF-8 без BOM при CsvEncoding = 1251 дає спотворені заголовки) описує поточну поведінку, а не бажану. Якщо колись Engine навчиться визначати кодування, очікування треба змінити свідомо.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>- Перший прогін може дати FAIL не лише через вади Engine, а й через неточність очікувань: кожен FAIL розбирається окремо.</t>
+          <t>Код запитів Engine не змінюється. Новий тестовий запит — файл у queries\ і рядок у test_All.</t>
         </is>
       </c>
     </row>
@@ -711,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1347,27 +1315,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X01</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TestXlsx</t>
+          <t>TestCsv</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>X01_table.xlsx</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>tblData</t>
+          <t>C18_legit_suffix.csv</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Місяць</t>
+          <t>Рік</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1376,14 +1339,14 @@
       <c r="L19" s="1" t="n"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Таблиця за іменем, рядок Всього</t>
+          <t>Законні колонки Назва і Назва_1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X02</t>
+          <t>X01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1393,12 +1356,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>X02_na_error.xlsx</t>
+          <t>X01_table.xlsx</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Аркуш1</t>
+          <t>tblData</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1407,19 +1370,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="1" t="n"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Аркуш, клітинка #N/A</t>
+          <t>Таблиця за іменем, рядок Всього</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X03</t>
+          <t>X02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1429,12 +1392,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>X03_wrong_sheet.xlsx</t>
+          <t>X02_na_error.xlsx</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>НемаТакого</t>
+          <t>Аркуш1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1443,19 +1406,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="1" t="n"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Неіснуючий TableSheetName</t>
+          <t>Аркуш, клітинка #N/A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X04</t>
+          <t>X03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1465,7 +1428,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>X04_ambiguous.xlsx</t>
+          <t>X03_wrong_sheet.xlsx</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>НемаТакого</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1474,19 +1442,19 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L22" s="1" t="n"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Два аркуші, TableSheetName порожнє</t>
+          <t>Неіснуючий TableSheetName</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X05</t>
+          <t>X04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1496,7 +1464,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>X05_corrupt.xlsx</t>
+          <t>X04_ambiguous.xlsx</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1505,19 +1473,19 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23" s="1" t="n"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Пошкоджений файл</t>
+          <t>Два аркуші, TableSheetName порожнє</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X06</t>
+          <t>X05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1527,7 +1495,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>X06_unsupported.json</t>
+          <t>X05_corrupt.xlsx</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1536,41 +1504,72 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L24" s="1" t="n"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Непідтримуване розширення</t>
+          <t>Пошкоджений файл</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N01</t>
+          <t>X06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TestNoSchema</t>
+          <t>TestXlsx</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>N01_no_schema.csv</t>
+          <t>X06_unsupported.json</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Місяць</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L25" s="1" t="n"/>
       <c r="M25" t="inlineStr">
+        <is>
+          <t>Непідтримуване розширення</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TestNoSchema</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>N01_no_schema.csv</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Рік</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1" t="n"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>Призначення без схеми</t>
         </is>
@@ -2170,7 +2169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2686,7 +2685,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X01</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2702,62 +2701,88 @@
       <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Назва_1 - окрема колонка, не дубль</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X02</t>
+          <t>X01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>5</v>
       </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>#N/A у джерелі</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X03</t>
+          <t>X02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>READ_ERROR</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>#N/A у джерелі</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X04</t>
+          <t>X03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2774,7 +2799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X05</t>
+          <t>X04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2791,7 +2816,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X06</t>
+          <t>X05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2808,15 +2833,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>X06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>READ_ERROR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>N01</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>NO_SCHEMA</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
